--- a/images/Employment.xlsx
+++ b/images/Employment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon.rhee\Desktop\gitpage\docs\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F78114-D07F-4740-88B9-80D805361B9B}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579B77A2-E87A-40F5-88EB-058681E70F48}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C666FD2C-32AC-43EC-BEA7-25CE32E05CBB}"/>
   </bookViews>
@@ -1061,9 +1061,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1"/>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -1695,9 +1693,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1"/>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>

--- a/images/Employment.xlsx
+++ b/images/Employment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon.rhee\Desktop\gitpage\docs\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579B77A2-E87A-40F5-88EB-058681E70F48}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860D0584-DB7A-42CA-BBF6-66F1491F75DA}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C666FD2C-32AC-43EC-BEA7-25CE32E05CBB}"/>
   </bookViews>
@@ -157,9 +157,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FF04AEE4"/>
       <color rgb="FF000032"/>
       <color rgb="FFE85811"/>
+      <color rgb="FF04AEE4"/>
       <color rgb="FFFFFFFF"/>
     </mruColors>
   </colors>
@@ -418,7 +418,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="04AEE4"/>
+                <a:srgbClr val="000032"/>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -475,7 +475,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="E85811"/>
+                <a:srgbClr val="04AEE4"/>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -485,6 +485,21 @@
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000028-4071-4C26-9BFF-A3CCA75DD1D4}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="E85811"/>
+              </a:solidFill>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001C-7603-41D6-B713-A140346D966A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1448,6 +1463,25 @@
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000011-FEC2-4124-A89A-0C8BDA511A44}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="9"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="000032"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000012-A604-4C1A-8464-AE50CBC7A95A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>

--- a/images/Employment.xlsx
+++ b/images/Employment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon.rhee\Desktop\gitpage\docs\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860D0584-DB7A-42CA-BBF6-66F1491F75DA}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D87FFE5-C3EC-4824-BAA6-37FEFB0AEDD0}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C666FD2C-32AC-43EC-BEA7-25CE32E05CBB}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>UCSD</t>
   </si>
@@ -113,6 +113,15 @@
   <si>
     <t>SQL</t>
   </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>Skills</t>
+  </si>
+  <si>
+    <t>Training</t>
+  </si>
 </sst>
 </file>
 
@@ -157,9 +166,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF04AEE4"/>
       <color rgb="FF000032"/>
       <color rgb="FFE85811"/>
-      <color rgb="FF04AEE4"/>
       <color rgb="FFFFFFFF"/>
     </mruColors>
   </colors>
@@ -1134,7 +1143,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Tools</a:t>
+              <a:t>Skillsets &amp; Tools</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1188,9 +1197,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$33:$B$42</c:f>
+              <c:f>Sheet1!$A$33:$B$44</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>AutoCAD</c:v>
@@ -1221,6 +1230,12 @@
                   </c:pt>
                   <c:pt idx="9">
                     <c:v>SAM</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Management</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Training</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -1232,6 +1247,9 @@
                   </c:pt>
                   <c:pt idx="6">
                     <c:v>Performance</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Skills</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -1239,10 +1257,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$33:$C$42</c:f>
+              <c:f>Sheet1!$C$33:$C$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>2015.5</c:v>
                 </c:pt>
@@ -1272,6 +1290,12 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2016.25</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2015.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1339,7 +1363,9 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="04AEE4"/>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -1358,7 +1384,9 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="04AEE4"/>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -1377,7 +1405,9 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="04AEE4"/>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -1396,7 +1426,9 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="04AEE4"/>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -1485,11 +1517,53 @@
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dPt>
+            <c:idx val="10"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-A047-4618-9985-C4D8F387856B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="11"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000014-A047-4618-9985-C4D8F387856B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$33:$B$42</c:f>
+              <c:f>Sheet1!$A$33:$B$44</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>AutoCAD</c:v>
@@ -1520,6 +1594,12 @@
                   </c:pt>
                   <c:pt idx="9">
                     <c:v>SAM</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Management</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Training</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -1531,6 +1611,9 @@
                   </c:pt>
                   <c:pt idx="6">
                     <c:v>Performance</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Skills</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -1538,10 +1621,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$33:$D$42</c:f>
+              <c:f>Sheet1!$D$33:$D$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>3.5</c:v>
                 </c:pt>
@@ -1571,6 +1654,12 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2671,7 +2760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F941FF5F-4D33-4F79-B6F3-DF0F8BA292C7}">
-  <dimension ref="A2:E42"/>
+  <dimension ref="A2:E44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -2882,7 +2971,7 @@
         <v>2010.75</v>
       </c>
       <c r="D35">
-        <f t="shared" ref="D35:D42" si="4">E35-C35</f>
+        <f t="shared" ref="D35:D43" si="4">E35-C35</f>
         <v>0.25</v>
       </c>
       <c r="E35">
@@ -2996,6 +3085,39 @@
         <v>1</v>
       </c>
       <c r="E42">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" t="s">
+        <v>28</v>
+      </c>
+      <c r="C43">
+        <v>2016.25</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="E43">
+        <v>2016.75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44">
+        <v>2015.75</v>
+      </c>
+      <c r="D44">
+        <f t="shared" ref="D44" si="5">E44-C44</f>
+        <v>3.25</v>
+      </c>
+      <c r="E44">
         <v>2019</v>
       </c>
     </row>

--- a/images/Employment.xlsx
+++ b/images/Employment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon.rhee\Desktop\gitpage\docs\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D87FFE5-C3EC-4824-BAA6-37FEFB0AEDD0}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D09E2C-F203-42BD-B5EF-EDAE4BF01E82}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C666FD2C-32AC-43EC-BEA7-25CE32E05CBB}"/>
   </bookViews>
@@ -588,7 +588,7 @@
                   <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.1666666666667425</c:v>
+                  <c:v>2.1666666666667425</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -941,7 +941,7 @@
                   <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.1666666666667425</c:v>
+                  <c:v>2.1666666666667425</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2909,10 +2909,10 @@
       </c>
       <c r="D10">
         <f t="shared" si="1"/>
-        <v>3.1666666666667425</v>
+        <v>2.1666666666667425</v>
       </c>
       <c r="E10">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="32" spans="3:5" x14ac:dyDescent="0.25">

--- a/images/Employment.xlsx
+++ b/images/Employment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon.rhee\Desktop\gitpage\docs\images\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\EDF\kurt-rhee.github.io\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D09E2C-F203-42BD-B5EF-EDAE4BF01E82}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B58248-7503-4F18-8FBC-A12615C014B7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C666FD2C-32AC-43EC-BEA7-25CE32E05CBB}"/>
   </bookViews>
@@ -20,7 +20,9 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>UCSD</t>
   </si>
@@ -122,6 +124,9 @@
   <si>
     <t>Training</t>
   </si>
+  <si>
+    <t>Sr. R&amp;D Engineer</t>
+  </si>
 </sst>
 </file>
 
@@ -166,9 +171,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFE85811"/>
       <color rgb="FF04AEE4"/>
       <color rgb="FF000032"/>
-      <color rgb="FFE85811"/>
       <color rgb="FFFFFFFF"/>
     </mruColors>
   </colors>
@@ -259,9 +264,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$3:$B$10</c:f>
+              <c:f>Sheet1!$A$3:$B$11</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>B.Sc. NanoEngineering</c:v>
@@ -286,6 +291,9 @@
                   </c:pt>
                   <c:pt idx="7">
                     <c:v>Solar Engineer</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Sr. R&amp;D Engineer</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -307,10 +315,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$3:$C$10</c:f>
+              <c:f>Sheet1!$C$3:$C$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>2010.75</c:v>
                 </c:pt>
@@ -334,6 +342,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2016.8333333333333</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2020.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -512,11 +523,29 @@
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="E85811"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001F-B223-4ED0-8F9A-CA4BE30C6C79}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$3:$B$10</c:f>
+              <c:f>Sheet1!$A$3:$B$11</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>B.Sc. NanoEngineering</c:v>
@@ -541,6 +570,9 @@
                   </c:pt>
                   <c:pt idx="7">
                     <c:v>Solar Engineer</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Sr. R&amp;D Engineer</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -562,10 +594,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$3:$D$10</c:f>
+              <c:f>Sheet1!$D$3:$D$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>4.75</c:v>
                 </c:pt>
@@ -588,7 +620,10 @@
                   <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.1666666666667425</c:v>
+                  <c:v>3.4166666666667425</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -623,9 +658,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$3:$B$10</c:f>
+              <c:f>Sheet1!$A$3:$B$11</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>B.Sc. NanoEngineering</c:v>
@@ -650,6 +685,9 @@
                   </c:pt>
                   <c:pt idx="7">
                     <c:v>Solar Engineer</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Sr. R&amp;D Engineer</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -671,10 +709,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$3:$C$10</c:f>
+              <c:f>Sheet1!$C$3:$C$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>2010.75</c:v>
                 </c:pt>
@@ -698,6 +736,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2016.8333333333333</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2020.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -867,9 +908,9 @@
           </c:dPt>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$3:$B$10</c:f>
+              <c:f>Sheet1!$A$3:$B$11</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>B.Sc. NanoEngineering</c:v>
@@ -894,6 +935,9 @@
                   </c:pt>
                   <c:pt idx="7">
                     <c:v>Solar Engineer</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Sr. R&amp;D Engineer</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -915,10 +959,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$3:$D$10</c:f>
+              <c:f>Sheet1!$D$3:$D$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>4.75</c:v>
                 </c:pt>
@@ -941,7 +985,10 @@
                   <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.1666666666667425</c:v>
+                  <c:v>3.4166666666667425</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -969,7 +1016,7 @@
         <c:axId val="492064128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="2020"/>
+          <c:max val="2021"/>
           <c:min val="2010"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -2389,14 +2436,14 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1466850</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:colOff>1514475</xdr:colOff>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>52386</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2859,7 +2906,7 @@
         <v>2015.5</v>
       </c>
       <c r="D7">
-        <f t="shared" ref="D7:D10" si="1">E7-C7</f>
+        <f t="shared" ref="D7:D11" si="1">E7-C7</f>
         <v>0.25</v>
       </c>
       <c r="E7">
@@ -2909,10 +2956,25 @@
       </c>
       <c r="D10">
         <f t="shared" si="1"/>
-        <v>2.1666666666667425</v>
+        <v>3.4166666666667425</v>
       </c>
       <c r="E10">
-        <v>2019</v>
+        <v>2020.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11">
+        <v>2020.25</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="E11">
+        <v>2021</v>
       </c>
     </row>
     <row r="32" spans="3:5" x14ac:dyDescent="0.25">
